--- a/examples/load-test/data/load-test.xlsx
+++ b/examples/load-test/data/load-test.xlsx
@@ -4468,10 +4468,10 @@
         <x:v>At vero eos et accusamus et iusto odio dignissimos ducimus qui blanditiis praesentium voluptatum deleniti atque corrupti.</x:v>
       </x:c>
       <x:c r="D2" s="18" t="str">
-        <x:v>assets/images/set-1/field-1/row-01.png</x:v>
+        <x:v>set-1_field-1_row-01.png</x:v>
       </x:c>
       <x:c r="E2" s="18" t="str">
-        <x:v>assets/images/set-1/field-2/row-01.png</x:v>
+        <x:v>set-1_field-2_row-01.png</x:v>
       </x:c>
       <x:c r="F2" s="19" t="n">
         <x:v>4</x:v>
@@ -4491,10 +4491,10 @@
         <x:v>Ut enim ad minima veniam, quis nostrum exercitationem ullam corporis suscipit laboriosam, nisi ut aliquid ex ea commodi consequatur.</x:v>
       </x:c>
       <x:c r="D3" s="18" t="str">
-        <x:v>assets/images/set-1/field-1/row-02.png</x:v>
+        <x:v>set-1_field-1_row-02.png</x:v>
       </x:c>
       <x:c r="E3" s="18" t="str">
-        <x:v>assets/images/set-1/field-2/row-02.png</x:v>
+        <x:v>set-1_field-2_row-02.png</x:v>
       </x:c>
       <x:c r="F3" s="19" t="n">
         <x:v>4</x:v>
@@ -4514,10 +4514,10 @@
         <x:v>Nam libero tempore, cum soluta nobis est eligendi optio cumque nihil impedit quo minus id quod maxime placeat facere possimus.</x:v>
       </x:c>
       <x:c r="D4" s="18" t="str">
-        <x:v>assets/images/set-1/field-1/row-03.png</x:v>
+        <x:v>set-1_field-1_row-03.png</x:v>
       </x:c>
       <x:c r="E4" s="18" t="str">
-        <x:v>assets/images/set-1/field-2/row-03.png</x:v>
+        <x:v>set-1_field-2_row-03.png</x:v>
       </x:c>
       <x:c r="F4" s="19" t="n">
         <x:v>4</x:v>
@@ -4537,10 +4537,10 @@
         <x:v>Lorem ipsum dolor sit amet, consectetur adipiscing elit, sed do eiusmod tempor incididunt ut labore et dolore magna aliqua.</x:v>
       </x:c>
       <x:c r="D5" s="18" t="str">
-        <x:v>assets/images/set-1/field-1/row-04.png</x:v>
+        <x:v>set-1_field-1_row-04.png</x:v>
       </x:c>
       <x:c r="E5" s="18" t="str">
-        <x:v>assets/images/set-1/field-2/row-04.png</x:v>
+        <x:v>set-1_field-2_row-04.png</x:v>
       </x:c>
       <x:c r="F5" s="19" t="n">
         <x:v>4</x:v>
@@ -4560,10 +4560,10 @@
         <x:v>Sed ut perspiciatis unde omnis iste natus error sit voluptatem accusantium doloremque laudantium, totam rem aperiam.</x:v>
       </x:c>
       <x:c r="D6" s="18" t="str">
-        <x:v>assets/images/set-1/field-1/row-05.png</x:v>
+        <x:v>set-1_field-1_row-05.png</x:v>
       </x:c>
       <x:c r="E6" s="18" t="str">
-        <x:v>assets/images/set-1/field-2/row-05.png</x:v>
+        <x:v>set-1_field-2_row-05.png</x:v>
       </x:c>
       <x:c r="F6" s="19" t="n">
         <x:v>4</x:v>
@@ -4583,10 +4583,10 @@
         <x:v>At vero eos et accusamus et iusto odio dignissimos ducimus qui blanditiis praesentium voluptatum deleniti atque corrupti.</x:v>
       </x:c>
       <x:c r="D7" s="18" t="str">
-        <x:v>assets/images/set-1/field-1/row-06.png</x:v>
+        <x:v>set-1_field-1_row-06.png</x:v>
       </x:c>
       <x:c r="E7" s="18" t="str">
-        <x:v>assets/images/set-1/field-2/row-06.png</x:v>
+        <x:v>set-1_field-2_row-06.png</x:v>
       </x:c>
       <x:c r="F7" s="19" t="n">
         <x:v>4</x:v>
@@ -4606,10 +4606,10 @@
         <x:v>Ut enim ad minima veniam, quis nostrum exercitationem ullam corporis suscipit laboriosam, nisi ut aliquid ex ea commodi consequatur.</x:v>
       </x:c>
       <x:c r="D8" s="18" t="str">
-        <x:v>assets/images/set-1/field-1/row-07.png</x:v>
+        <x:v>set-1_field-1_row-07.png</x:v>
       </x:c>
       <x:c r="E8" s="18" t="str">
-        <x:v>assets/images/set-1/field-2/row-07.png</x:v>
+        <x:v>set-1_field-2_row-07.png</x:v>
       </x:c>
       <x:c r="F8" s="19" t="n">
         <x:v>4</x:v>
@@ -4629,10 +4629,10 @@
         <x:v>Nam libero tempore, cum soluta nobis est eligendi optio cumque nihil impedit quo minus id quod maxime placeat facere possimus.</x:v>
       </x:c>
       <x:c r="D9" s="18" t="str">
-        <x:v>assets/images/set-1/field-1/row-08.png</x:v>
+        <x:v>set-1_field-1_row-08.png</x:v>
       </x:c>
       <x:c r="E9" s="18" t="str">
-        <x:v>assets/images/set-1/field-2/row-08.png</x:v>
+        <x:v>set-1_field-2_row-08.png</x:v>
       </x:c>
       <x:c r="F9" s="19" t="n">
         <x:v>4</x:v>
@@ -4652,10 +4652,10 @@
         <x:v>Lorem ipsum dolor sit amet, consectetur adipiscing elit, sed do eiusmod tempor incididunt ut labore et dolore magna aliqua.</x:v>
       </x:c>
       <x:c r="D10" s="18" t="str">
-        <x:v>assets/images/set-1/field-1/row-09.png</x:v>
+        <x:v>set-1_field-1_row-09.png</x:v>
       </x:c>
       <x:c r="E10" s="18" t="str">
-        <x:v>assets/images/set-1/field-2/row-09.png</x:v>
+        <x:v>set-1_field-2_row-09.png</x:v>
       </x:c>
       <x:c r="F10" s="19" t="n">
         <x:v>4</x:v>
@@ -4675,10 +4675,10 @@
         <x:v>Sed ut perspiciatis unde omnis iste natus error sit voluptatem accusantium doloremque laudantium, totam rem aperiam.</x:v>
       </x:c>
       <x:c r="D11" s="18" t="str">
-        <x:v>assets/images/set-1/field-1/row-10.png</x:v>
+        <x:v>set-1_field-1_row-10.png</x:v>
       </x:c>
       <x:c r="E11" s="18" t="str">
-        <x:v>assets/images/set-1/field-2/row-10.png</x:v>
+        <x:v>set-1_field-2_row-10.png</x:v>
       </x:c>
       <x:c r="F11" s="19" t="n">
         <x:v>4</x:v>
@@ -4698,10 +4698,10 @@
         <x:v>At vero eos et accusamus et iusto odio dignissimos ducimus qui blanditiis praesentium voluptatum deleniti atque corrupti.</x:v>
       </x:c>
       <x:c r="D12" s="18" t="str">
-        <x:v>assets/images/set-1/field-1/row-11.png</x:v>
+        <x:v>set-1_field-1_row-11.png</x:v>
       </x:c>
       <x:c r="E12" s="18" t="str">
-        <x:v>assets/images/set-1/field-2/row-11.png</x:v>
+        <x:v>set-1_field-2_row-11.png</x:v>
       </x:c>
       <x:c r="F12" s="19" t="n">
         <x:v>4</x:v>
@@ -4721,10 +4721,10 @@
         <x:v>Ut enim ad minima veniam, quis nostrum exercitationem ullam corporis suscipit laboriosam, nisi ut aliquid ex ea commodi consequatur.</x:v>
       </x:c>
       <x:c r="D13" s="18" t="str">
-        <x:v>assets/images/set-1/field-1/row-12.png</x:v>
+        <x:v>set-1_field-1_row-12.png</x:v>
       </x:c>
       <x:c r="E13" s="18" t="str">
-        <x:v>assets/images/set-1/field-2/row-12.png</x:v>
+        <x:v>set-1_field-2_row-12.png</x:v>
       </x:c>
       <x:c r="F13" s="19" t="n">
         <x:v>4</x:v>
@@ -4744,10 +4744,10 @@
         <x:v>Nam libero tempore, cum soluta nobis est eligendi optio cumque nihil impedit quo minus id quod maxime placeat facere possimus.</x:v>
       </x:c>
       <x:c r="D14" s="18" t="str">
-        <x:v>assets/images/set-1/field-1/row-13.png</x:v>
+        <x:v>set-1_field-1_row-13.png</x:v>
       </x:c>
       <x:c r="E14" s="18" t="str">
-        <x:v>assets/images/set-1/field-2/row-13.png</x:v>
+        <x:v>set-1_field-2_row-13.png</x:v>
       </x:c>
       <x:c r="F14" s="19" t="n">
         <x:v>4</x:v>
@@ -4767,10 +4767,10 @@
         <x:v>Lorem ipsum dolor sit amet, consectetur adipiscing elit, sed do eiusmod tempor incididunt ut labore et dolore magna aliqua.</x:v>
       </x:c>
       <x:c r="D15" s="18" t="str">
-        <x:v>assets/images/set-1/field-1/row-14.png</x:v>
+        <x:v>set-1_field-1_row-14.png</x:v>
       </x:c>
       <x:c r="E15" s="18" t="str">
-        <x:v>assets/images/set-1/field-2/row-14.png</x:v>
+        <x:v>set-1_field-2_row-14.png</x:v>
       </x:c>
       <x:c r="F15" s="19" t="n">
         <x:v>4</x:v>
@@ -4790,10 +4790,10 @@
         <x:v>Sed ut perspiciatis unde omnis iste natus error sit voluptatem accusantium doloremque laudantium, totam rem aperiam.</x:v>
       </x:c>
       <x:c r="D16" s="18" t="str">
-        <x:v>assets/images/set-1/field-1/row-15.png</x:v>
+        <x:v>set-1_field-1_row-15.png</x:v>
       </x:c>
       <x:c r="E16" s="18" t="str">
-        <x:v>assets/images/set-1/field-2/row-15.png</x:v>
+        <x:v>set-1_field-2_row-15.png</x:v>
       </x:c>
       <x:c r="F16" s="19" t="n">
         <x:v>4</x:v>
@@ -4813,10 +4813,10 @@
         <x:v>At vero eos et accusamus et iusto odio dignissimos ducimus qui blanditiis praesentium voluptatum deleniti atque corrupti.</x:v>
       </x:c>
       <x:c r="D17" s="18" t="str">
-        <x:v>assets/images/set-1/field-1/row-16.png</x:v>
+        <x:v>set-1_field-1_row-16.png</x:v>
       </x:c>
       <x:c r="E17" s="18" t="str">
-        <x:v>assets/images/set-1/field-2/row-16.png</x:v>
+        <x:v>set-1_field-2_row-16.png</x:v>
       </x:c>
       <x:c r="F17" s="19" t="n">
         <x:v>4</x:v>
@@ -4836,10 +4836,10 @@
         <x:v>Ut enim ad minima veniam, quis nostrum exercitationem ullam corporis suscipit laboriosam, nisi ut aliquid ex ea commodi consequatur.</x:v>
       </x:c>
       <x:c r="D18" s="18" t="str">
-        <x:v>assets/images/set-1/field-1/row-17.png</x:v>
+        <x:v>set-1_field-1_row-17.png</x:v>
       </x:c>
       <x:c r="E18" s="18" t="str">
-        <x:v>assets/images/set-1/field-2/row-17.png</x:v>
+        <x:v>set-1_field-2_row-17.png</x:v>
       </x:c>
       <x:c r="F18" s="19" t="n">
         <x:v>4</x:v>
@@ -4859,10 +4859,10 @@
         <x:v>Nam libero tempore, cum soluta nobis est eligendi optio cumque nihil impedit quo minus id quod maxime placeat facere possimus.</x:v>
       </x:c>
       <x:c r="D19" s="18" t="str">
-        <x:v>assets/images/set-1/field-1/row-18.png</x:v>
+        <x:v>set-1_field-1_row-18.png</x:v>
       </x:c>
       <x:c r="E19" s="18" t="str">
-        <x:v>assets/images/set-1/field-2/row-18.png</x:v>
+        <x:v>set-1_field-2_row-18.png</x:v>
       </x:c>
       <x:c r="F19" s="19" t="n">
         <x:v>4</x:v>
@@ -4882,10 +4882,10 @@
         <x:v>Lorem ipsum dolor sit amet, consectetur adipiscing elit, sed do eiusmod tempor incididunt ut labore et dolore magna aliqua.</x:v>
       </x:c>
       <x:c r="D20" s="18" t="str">
-        <x:v>assets/images/set-1/field-1/row-19.png</x:v>
+        <x:v>set-1_field-1_row-19.png</x:v>
       </x:c>
       <x:c r="E20" s="18" t="str">
-        <x:v>assets/images/set-1/field-2/row-19.png</x:v>
+        <x:v>set-1_field-2_row-19.png</x:v>
       </x:c>
       <x:c r="F20" s="19" t="n">
         <x:v>4</x:v>
@@ -4905,10 +4905,10 @@
         <x:v>Sed ut perspiciatis unde omnis iste natus error sit voluptatem accusantium doloremque laudantium, totam rem aperiam.</x:v>
       </x:c>
       <x:c r="D21" s="18" t="str">
-        <x:v>assets/images/set-1/field-1/row-20.png</x:v>
+        <x:v>set-1_field-1_row-20.png</x:v>
       </x:c>
       <x:c r="E21" s="18" t="str">
-        <x:v>assets/images/set-1/field-2/row-20.png</x:v>
+        <x:v>set-1_field-2_row-20.png</x:v>
       </x:c>
       <x:c r="F21" s="19" t="n">
         <x:v>4</x:v>
@@ -4928,10 +4928,10 @@
         <x:v>At vero eos et accusamus et iusto odio dignissimos ducimus qui blanditiis praesentium voluptatum deleniti atque corrupti.</x:v>
       </x:c>
       <x:c r="D22" s="18" t="str">
-        <x:v>assets/images/set-1/field-1/row-21.png</x:v>
+        <x:v>set-1_field-1_row-21.png</x:v>
       </x:c>
       <x:c r="E22" s="18" t="str">
-        <x:v>assets/images/set-1/field-2/row-21.png</x:v>
+        <x:v>set-1_field-2_row-21.png</x:v>
       </x:c>
       <x:c r="F22" s="19" t="n">
         <x:v>4</x:v>
@@ -4951,10 +4951,10 @@
         <x:v>Ut enim ad minima veniam, quis nostrum exercitationem ullam corporis suscipit laboriosam, nisi ut aliquid ex ea commodi consequatur.</x:v>
       </x:c>
       <x:c r="D23" s="18" t="str">
-        <x:v>assets/images/set-1/field-1/row-22.png</x:v>
+        <x:v>set-1_field-1_row-22.png</x:v>
       </x:c>
       <x:c r="E23" s="18" t="str">
-        <x:v>assets/images/set-1/field-2/row-22.png</x:v>
+        <x:v>set-1_field-2_row-22.png</x:v>
       </x:c>
       <x:c r="F23" s="19" t="n">
         <x:v>4</x:v>
@@ -4974,10 +4974,10 @@
         <x:v>Nam libero tempore, cum soluta nobis est eligendi optio cumque nihil impedit quo minus id quod maxime placeat facere possimus.</x:v>
       </x:c>
       <x:c r="D24" s="18" t="str">
-        <x:v>assets/images/set-1/field-1/row-23.png</x:v>
+        <x:v>set-1_field-1_row-23.png</x:v>
       </x:c>
       <x:c r="E24" s="18" t="str">
-        <x:v>assets/images/set-1/field-2/row-23.png</x:v>
+        <x:v>set-1_field-2_row-23.png</x:v>
       </x:c>
       <x:c r="F24" s="19" t="n">
         <x:v>4</x:v>
@@ -4997,10 +4997,10 @@
         <x:v>Lorem ipsum dolor sit amet, consectetur adipiscing elit, sed do eiusmod tempor incididunt ut labore et dolore magna aliqua.</x:v>
       </x:c>
       <x:c r="D25" s="18" t="str">
-        <x:v>assets/images/set-1/field-1/row-24.png</x:v>
+        <x:v>set-1_field-1_row-24.png</x:v>
       </x:c>
       <x:c r="E25" s="18" t="str">
-        <x:v>assets/images/set-1/field-2/row-24.png</x:v>
+        <x:v>set-1_field-2_row-24.png</x:v>
       </x:c>
       <x:c r="F25" s="19" t="n">
         <x:v>4</x:v>
@@ -5020,10 +5020,10 @@
         <x:v>Sed ut perspiciatis unde omnis iste natus error sit voluptatem accusantium doloremque laudantium, totam rem aperiam.</x:v>
       </x:c>
       <x:c r="D26" s="21" t="str">
-        <x:v>assets/images/set-1/field-1/row-25.png</x:v>
+        <x:v>set-1_field-1_row-25.png</x:v>
       </x:c>
       <x:c r="E26" s="21" t="str">
-        <x:v>assets/images/set-1/field-2/row-25.png</x:v>
+        <x:v>set-1_field-2_row-25.png</x:v>
       </x:c>
       <x:c r="F26" s="22" t="n">
         <x:v>4</x:v>
@@ -5085,10 +5085,10 @@
         <x:v>At vero eos et accusamus et iusto odio dignissimos ducimus qui blanditiis praesentium voluptatum deleniti atque corrupti.</x:v>
       </x:c>
       <x:c r="D2" s="18" t="str">
-        <x:v>assets/images/set-2/field-1/row-01.png</x:v>
+        <x:v>set-2_field-1_row-01.png</x:v>
       </x:c>
       <x:c r="E2" s="18" t="str">
-        <x:v>assets/images/set-2/field-2/row-01.png</x:v>
+        <x:v>set-2_field-2_row-01.png</x:v>
       </x:c>
       <x:c r="F2" s="19" t="n">
         <x:v>4</x:v>
@@ -5108,10 +5108,10 @@
         <x:v>Ut enim ad minima veniam, quis nostrum exercitationem ullam corporis suscipit laboriosam, nisi ut aliquid ex ea commodi consequatur.</x:v>
       </x:c>
       <x:c r="D3" s="18" t="str">
-        <x:v>assets/images/set-2/field-1/row-02.png</x:v>
+        <x:v>set-2_field-1_row-02.png</x:v>
       </x:c>
       <x:c r="E3" s="18" t="str">
-        <x:v>assets/images/set-2/field-2/row-02.png</x:v>
+        <x:v>set-2_field-2_row-02.png</x:v>
       </x:c>
       <x:c r="F3" s="19" t="n">
         <x:v>4</x:v>
@@ -5131,10 +5131,10 @@
         <x:v>Nam libero tempore, cum soluta nobis est eligendi optio cumque nihil impedit quo minus id quod maxime placeat facere possimus.</x:v>
       </x:c>
       <x:c r="D4" s="18" t="str">
-        <x:v>assets/images/set-2/field-1/row-03.png</x:v>
+        <x:v>set-2_field-1_row-03.png</x:v>
       </x:c>
       <x:c r="E4" s="18" t="str">
-        <x:v>assets/images/set-2/field-2/row-03.png</x:v>
+        <x:v>set-2_field-2_row-03.png</x:v>
       </x:c>
       <x:c r="F4" s="19" t="n">
         <x:v>4</x:v>
@@ -5154,10 +5154,10 @@
         <x:v>Lorem ipsum dolor sit amet, consectetur adipiscing elit, sed do eiusmod tempor incididunt ut labore et dolore magna aliqua.</x:v>
       </x:c>
       <x:c r="D5" s="18" t="str">
-        <x:v>assets/images/set-2/field-1/row-04.png</x:v>
+        <x:v>set-2_field-1_row-04.png</x:v>
       </x:c>
       <x:c r="E5" s="18" t="str">
-        <x:v>assets/images/set-2/field-2/row-04.png</x:v>
+        <x:v>set-2_field-2_row-04.png</x:v>
       </x:c>
       <x:c r="F5" s="19" t="n">
         <x:v>4</x:v>
@@ -5177,10 +5177,10 @@
         <x:v>Sed ut perspiciatis unde omnis iste natus error sit voluptatem accusantium doloremque laudantium, totam rem aperiam.</x:v>
       </x:c>
       <x:c r="D6" s="18" t="str">
-        <x:v>assets/images/set-2/field-1/row-05.png</x:v>
+        <x:v>set-2_field-1_row-05.png</x:v>
       </x:c>
       <x:c r="E6" s="18" t="str">
-        <x:v>assets/images/set-2/field-2/row-05.png</x:v>
+        <x:v>set-2_field-2_row-05.png</x:v>
       </x:c>
       <x:c r="F6" s="19" t="n">
         <x:v>4</x:v>
@@ -5200,10 +5200,10 @@
         <x:v>At vero eos et accusamus et iusto odio dignissimos ducimus qui blanditiis praesentium voluptatum deleniti atque corrupti.</x:v>
       </x:c>
       <x:c r="D7" s="18" t="str">
-        <x:v>assets/images/set-2/field-1/row-06.png</x:v>
+        <x:v>set-2_field-1_row-06.png</x:v>
       </x:c>
       <x:c r="E7" s="18" t="str">
-        <x:v>assets/images/set-2/field-2/row-06.png</x:v>
+        <x:v>set-2_field-2_row-06.png</x:v>
       </x:c>
       <x:c r="F7" s="19" t="n">
         <x:v>4</x:v>
@@ -5223,10 +5223,10 @@
         <x:v>Ut enim ad minima veniam, quis nostrum exercitationem ullam corporis suscipit laboriosam, nisi ut aliquid ex ea commodi consequatur.</x:v>
       </x:c>
       <x:c r="D8" s="18" t="str">
-        <x:v>assets/images/set-2/field-1/row-07.png</x:v>
+        <x:v>set-2_field-1_row-07.png</x:v>
       </x:c>
       <x:c r="E8" s="18" t="str">
-        <x:v>assets/images/set-2/field-2/row-07.png</x:v>
+        <x:v>set-2_field-2_row-07.png</x:v>
       </x:c>
       <x:c r="F8" s="19" t="n">
         <x:v>4</x:v>
@@ -5246,10 +5246,10 @@
         <x:v>Nam libero tempore, cum soluta nobis est eligendi optio cumque nihil impedit quo minus id quod maxime placeat facere possimus.</x:v>
       </x:c>
       <x:c r="D9" s="18" t="str">
-        <x:v>assets/images/set-2/field-1/row-08.png</x:v>
+        <x:v>set-2_field-1_row-08.png</x:v>
       </x:c>
       <x:c r="E9" s="18" t="str">
-        <x:v>assets/images/set-2/field-2/row-08.png</x:v>
+        <x:v>set-2_field-2_row-08.png</x:v>
       </x:c>
       <x:c r="F9" s="19" t="n">
         <x:v>4</x:v>
@@ -5269,10 +5269,10 @@
         <x:v>Lorem ipsum dolor sit amet, consectetur adipiscing elit, sed do eiusmod tempor incididunt ut labore et dolore magna aliqua.</x:v>
       </x:c>
       <x:c r="D10" s="18" t="str">
-        <x:v>assets/images/set-2/field-1/row-09.png</x:v>
+        <x:v>set-2_field-1_row-09.png</x:v>
       </x:c>
       <x:c r="E10" s="18" t="str">
-        <x:v>assets/images/set-2/field-2/row-09.png</x:v>
+        <x:v>set-2_field-2_row-09.png</x:v>
       </x:c>
       <x:c r="F10" s="19" t="n">
         <x:v>4</x:v>
@@ -5292,10 +5292,10 @@
         <x:v>Sed ut perspiciatis unde omnis iste natus error sit voluptatem accusantium doloremque laudantium, totam rem aperiam.</x:v>
       </x:c>
       <x:c r="D11" s="18" t="str">
-        <x:v>assets/images/set-2/field-1/row-10.png</x:v>
+        <x:v>set-2_field-1_row-10.png</x:v>
       </x:c>
       <x:c r="E11" s="18" t="str">
-        <x:v>assets/images/set-2/field-2/row-10.png</x:v>
+        <x:v>set-2_field-2_row-10.png</x:v>
       </x:c>
       <x:c r="F11" s="19" t="n">
         <x:v>4</x:v>
@@ -5315,10 +5315,10 @@
         <x:v>At vero eos et accusamus et iusto odio dignissimos ducimus qui blanditiis praesentium voluptatum deleniti atque corrupti.</x:v>
       </x:c>
       <x:c r="D12" s="18" t="str">
-        <x:v>assets/images/set-2/field-1/row-11.png</x:v>
+        <x:v>set-2_field-1_row-11.png</x:v>
       </x:c>
       <x:c r="E12" s="18" t="str">
-        <x:v>assets/images/set-2/field-2/row-11.png</x:v>
+        <x:v>set-2_field-2_row-11.png</x:v>
       </x:c>
       <x:c r="F12" s="19" t="n">
         <x:v>4</x:v>
@@ -5338,10 +5338,10 @@
         <x:v>Ut enim ad minima veniam, quis nostrum exercitationem ullam corporis suscipit laboriosam, nisi ut aliquid ex ea commodi consequatur.</x:v>
       </x:c>
       <x:c r="D13" s="18" t="str">
-        <x:v>assets/images/set-2/field-1/row-12.png</x:v>
+        <x:v>set-2_field-1_row-12.png</x:v>
       </x:c>
       <x:c r="E13" s="18" t="str">
-        <x:v>assets/images/set-2/field-2/row-12.png</x:v>
+        <x:v>set-2_field-2_row-12.png</x:v>
       </x:c>
       <x:c r="F13" s="19" t="n">
         <x:v>4</x:v>
@@ -5361,10 +5361,10 @@
         <x:v>Nam libero tempore, cum soluta nobis est eligendi optio cumque nihil impedit quo minus id quod maxime placeat facere possimus.</x:v>
       </x:c>
       <x:c r="D14" s="18" t="str">
-        <x:v>assets/images/set-2/field-1/row-13.png</x:v>
+        <x:v>set-2_field-1_row-13.png</x:v>
       </x:c>
       <x:c r="E14" s="18" t="str">
-        <x:v>assets/images/set-2/field-2/row-13.png</x:v>
+        <x:v>set-2_field-2_row-13.png</x:v>
       </x:c>
       <x:c r="F14" s="19" t="n">
         <x:v>4</x:v>
@@ -5384,10 +5384,10 @@
         <x:v>Lorem ipsum dolor sit amet, consectetur adipiscing elit, sed do eiusmod tempor incididunt ut labore et dolore magna aliqua.</x:v>
       </x:c>
       <x:c r="D15" s="18" t="str">
-        <x:v>assets/images/set-2/field-1/row-14.png</x:v>
+        <x:v>set-2_field-1_row-14.png</x:v>
       </x:c>
       <x:c r="E15" s="18" t="str">
-        <x:v>assets/images/set-2/field-2/row-14.png</x:v>
+        <x:v>set-2_field-2_row-14.png</x:v>
       </x:c>
       <x:c r="F15" s="19" t="n">
         <x:v>4</x:v>
@@ -5407,10 +5407,10 @@
         <x:v>Sed ut perspiciatis unde omnis iste natus error sit voluptatem accusantium doloremque laudantium, totam rem aperiam.</x:v>
       </x:c>
       <x:c r="D16" s="18" t="str">
-        <x:v>assets/images/set-2/field-1/row-15.png</x:v>
+        <x:v>set-2_field-1_row-15.png</x:v>
       </x:c>
       <x:c r="E16" s="18" t="str">
-        <x:v>assets/images/set-2/field-2/row-15.png</x:v>
+        <x:v>set-2_field-2_row-15.png</x:v>
       </x:c>
       <x:c r="F16" s="19" t="n">
         <x:v>4</x:v>
@@ -5430,10 +5430,10 @@
         <x:v>At vero eos et accusamus et iusto odio dignissimos ducimus qui blanditiis praesentium voluptatum deleniti atque corrupti.</x:v>
       </x:c>
       <x:c r="D17" s="18" t="str">
-        <x:v>assets/images/set-2/field-1/row-16.png</x:v>
+        <x:v>set-2_field-1_row-16.png</x:v>
       </x:c>
       <x:c r="E17" s="18" t="str">
-        <x:v>assets/images/set-2/field-2/row-16.png</x:v>
+        <x:v>set-2_field-2_row-16.png</x:v>
       </x:c>
       <x:c r="F17" s="19" t="n">
         <x:v>4</x:v>
@@ -5453,10 +5453,10 @@
         <x:v>Ut enim ad minima veniam, quis nostrum exercitationem ullam corporis suscipit laboriosam, nisi ut aliquid ex ea commodi consequatur.</x:v>
       </x:c>
       <x:c r="D18" s="18" t="str">
-        <x:v>assets/images/set-2/field-1/row-17.png</x:v>
+        <x:v>set-2_field-1_row-17.png</x:v>
       </x:c>
       <x:c r="E18" s="18" t="str">
-        <x:v>assets/images/set-2/field-2/row-17.png</x:v>
+        <x:v>set-2_field-2_row-17.png</x:v>
       </x:c>
       <x:c r="F18" s="19" t="n">
         <x:v>4</x:v>
@@ -5476,10 +5476,10 @@
         <x:v>Nam libero tempore, cum soluta nobis est eligendi optio cumque nihil impedit quo minus id quod maxime placeat facere possimus.</x:v>
       </x:c>
       <x:c r="D19" s="18" t="str">
-        <x:v>assets/images/set-2/field-1/row-18.png</x:v>
+        <x:v>set-2_field-1_row-18.png</x:v>
       </x:c>
       <x:c r="E19" s="18" t="str">
-        <x:v>assets/images/set-2/field-2/row-18.png</x:v>
+        <x:v>set-2_field-2_row-18.png</x:v>
       </x:c>
       <x:c r="F19" s="19" t="n">
         <x:v>4</x:v>
@@ -5499,10 +5499,10 @@
         <x:v>Lorem ipsum dolor sit amet, consectetur adipiscing elit, sed do eiusmod tempor incididunt ut labore et dolore magna aliqua.</x:v>
       </x:c>
       <x:c r="D20" s="18" t="str">
-        <x:v>assets/images/set-2/field-1/row-19.png</x:v>
+        <x:v>set-2_field-1_row-19.png</x:v>
       </x:c>
       <x:c r="E20" s="18" t="str">
-        <x:v>assets/images/set-2/field-2/row-19.png</x:v>
+        <x:v>set-2_field-2_row-19.png</x:v>
       </x:c>
       <x:c r="F20" s="19" t="n">
         <x:v>4</x:v>
@@ -5522,10 +5522,10 @@
         <x:v>Sed ut perspiciatis unde omnis iste natus error sit voluptatem accusantium doloremque laudantium, totam rem aperiam.</x:v>
       </x:c>
       <x:c r="D21" s="18" t="str">
-        <x:v>assets/images/set-2/field-1/row-20.png</x:v>
+        <x:v>set-2_field-1_row-20.png</x:v>
       </x:c>
       <x:c r="E21" s="18" t="str">
-        <x:v>assets/images/set-2/field-2/row-20.png</x:v>
+        <x:v>set-2_field-2_row-20.png</x:v>
       </x:c>
       <x:c r="F21" s="19" t="n">
         <x:v>4</x:v>
@@ -5545,10 +5545,10 @@
         <x:v>At vero eos et accusamus et iusto odio dignissimos ducimus qui blanditiis praesentium voluptatum deleniti atque corrupti.</x:v>
       </x:c>
       <x:c r="D22" s="18" t="str">
-        <x:v>assets/images/set-2/field-1/row-21.png</x:v>
+        <x:v>set-2_field-1_row-21.png</x:v>
       </x:c>
       <x:c r="E22" s="18" t="str">
-        <x:v>assets/images/set-2/field-2/row-21.png</x:v>
+        <x:v>set-2_field-2_row-21.png</x:v>
       </x:c>
       <x:c r="F22" s="19" t="n">
         <x:v>4</x:v>
@@ -5568,10 +5568,10 @@
         <x:v>Ut enim ad minima veniam, quis nostrum exercitationem ullam corporis suscipit laboriosam, nisi ut aliquid ex ea commodi consequatur.</x:v>
       </x:c>
       <x:c r="D23" s="18" t="str">
-        <x:v>assets/images/set-2/field-1/row-22.png</x:v>
+        <x:v>set-2_field-1_row-22.png</x:v>
       </x:c>
       <x:c r="E23" s="18" t="str">
-        <x:v>assets/images/set-2/field-2/row-22.png</x:v>
+        <x:v>set-2_field-2_row-22.png</x:v>
       </x:c>
       <x:c r="F23" s="19" t="n">
         <x:v>4</x:v>
@@ -5591,10 +5591,10 @@
         <x:v>Nam libero tempore, cum soluta nobis est eligendi optio cumque nihil impedit quo minus id quod maxime placeat facere possimus.</x:v>
       </x:c>
       <x:c r="D24" s="18" t="str">
-        <x:v>assets/images/set-2/field-1/row-23.png</x:v>
+        <x:v>set-2_field-1_row-23.png</x:v>
       </x:c>
       <x:c r="E24" s="18" t="str">
-        <x:v>assets/images/set-2/field-2/row-23.png</x:v>
+        <x:v>set-2_field-2_row-23.png</x:v>
       </x:c>
       <x:c r="F24" s="19" t="n">
         <x:v>4</x:v>
@@ -5614,10 +5614,10 @@
         <x:v>Lorem ipsum dolor sit amet, consectetur adipiscing elit, sed do eiusmod tempor incididunt ut labore et dolore magna aliqua.</x:v>
       </x:c>
       <x:c r="D25" s="18" t="str">
-        <x:v>assets/images/set-2/field-1/row-24.png</x:v>
+        <x:v>set-2_field-1_row-24.png</x:v>
       </x:c>
       <x:c r="E25" s="18" t="str">
-        <x:v>assets/images/set-2/field-2/row-24.png</x:v>
+        <x:v>set-2_field-2_row-24.png</x:v>
       </x:c>
       <x:c r="F25" s="19" t="n">
         <x:v>4</x:v>
@@ -5637,10 +5637,10 @@
         <x:v>Sed ut perspiciatis unde omnis iste natus error sit voluptatem accusantium doloremque laudantium, totam rem aperiam.</x:v>
       </x:c>
       <x:c r="D26" s="21" t="str">
-        <x:v>assets/images/set-2/field-1/row-25.png</x:v>
+        <x:v>set-2_field-1_row-25.png</x:v>
       </x:c>
       <x:c r="E26" s="21" t="str">
-        <x:v>assets/images/set-2/field-2/row-25.png</x:v>
+        <x:v>set-2_field-2_row-25.png</x:v>
       </x:c>
       <x:c r="F26" s="22" t="n">
         <x:v>4</x:v>
@@ -5702,10 +5702,10 @@
         <x:v>At vero eos et accusamus et iusto odio dignissimos ducimus qui blanditiis praesentium voluptatum deleniti atque corrupti.</x:v>
       </x:c>
       <x:c r="D2" s="18" t="str">
-        <x:v>assets/images/set-3/field-1/row-01.png</x:v>
+        <x:v>set-3_field-1_row-01.png</x:v>
       </x:c>
       <x:c r="E2" s="18" t="str">
-        <x:v>assets/images/set-3/field-2/row-01.png</x:v>
+        <x:v>set-3_field-2_row-01.png</x:v>
       </x:c>
       <x:c r="F2" s="19" t="n">
         <x:v>4</x:v>
@@ -5725,10 +5725,10 @@
         <x:v>Ut enim ad minima veniam, quis nostrum exercitationem ullam corporis suscipit laboriosam, nisi ut aliquid ex ea commodi consequatur.</x:v>
       </x:c>
       <x:c r="D3" s="18" t="str">
-        <x:v>assets/images/set-3/field-1/row-02.png</x:v>
+        <x:v>set-3_field-1_row-02.png</x:v>
       </x:c>
       <x:c r="E3" s="18" t="str">
-        <x:v>assets/images/set-3/field-2/row-02.png</x:v>
+        <x:v>set-3_field-2_row-02.png</x:v>
       </x:c>
       <x:c r="F3" s="19" t="n">
         <x:v>4</x:v>
@@ -5748,10 +5748,10 @@
         <x:v>Nam libero tempore, cum soluta nobis est eligendi optio cumque nihil impedit quo minus id quod maxime placeat facere possimus.</x:v>
       </x:c>
       <x:c r="D4" s="18" t="str">
-        <x:v>assets/images/set-3/field-1/row-03.png</x:v>
+        <x:v>set-3_field-1_row-03.png</x:v>
       </x:c>
       <x:c r="E4" s="18" t="str">
-        <x:v>assets/images/set-3/field-2/row-03.png</x:v>
+        <x:v>set-3_field-2_row-03.png</x:v>
       </x:c>
       <x:c r="F4" s="19" t="n">
         <x:v>4</x:v>
@@ -5771,10 +5771,10 @@
         <x:v>Lorem ipsum dolor sit amet, consectetur adipiscing elit, sed do eiusmod tempor incididunt ut labore et dolore magna aliqua.</x:v>
       </x:c>
       <x:c r="D5" s="18" t="str">
-        <x:v>assets/images/set-3/field-1/row-04.png</x:v>
+        <x:v>set-3_field-1_row-04.png</x:v>
       </x:c>
       <x:c r="E5" s="18" t="str">
-        <x:v>assets/images/set-3/field-2/row-04.png</x:v>
+        <x:v>set-3_field-2_row-04.png</x:v>
       </x:c>
       <x:c r="F5" s="19" t="n">
         <x:v>4</x:v>
@@ -5794,10 +5794,10 @@
         <x:v>Sed ut perspiciatis unde omnis iste natus error sit voluptatem accusantium doloremque laudantium, totam rem aperiam.</x:v>
       </x:c>
       <x:c r="D6" s="18" t="str">
-        <x:v>assets/images/set-3/field-1/row-05.png</x:v>
+        <x:v>set-3_field-1_row-05.png</x:v>
       </x:c>
       <x:c r="E6" s="18" t="str">
-        <x:v>assets/images/set-3/field-2/row-05.png</x:v>
+        <x:v>set-3_field-2_row-05.png</x:v>
       </x:c>
       <x:c r="F6" s="19" t="n">
         <x:v>4</x:v>
@@ -5817,10 +5817,10 @@
         <x:v>At vero eos et accusamus et iusto odio dignissimos ducimus qui blanditiis praesentium voluptatum deleniti atque corrupti.</x:v>
       </x:c>
       <x:c r="D7" s="18" t="str">
-        <x:v>assets/images/set-3/field-1/row-06.png</x:v>
+        <x:v>set-3_field-1_row-06.png</x:v>
       </x:c>
       <x:c r="E7" s="18" t="str">
-        <x:v>assets/images/set-3/field-2/row-06.png</x:v>
+        <x:v>set-3_field-2_row-06.png</x:v>
       </x:c>
       <x:c r="F7" s="19" t="n">
         <x:v>4</x:v>
@@ -5840,10 +5840,10 @@
         <x:v>Ut enim ad minima veniam, quis nostrum exercitationem ullam corporis suscipit laboriosam, nisi ut aliquid ex ea commodi consequatur.</x:v>
       </x:c>
       <x:c r="D8" s="18" t="str">
-        <x:v>assets/images/set-3/field-1/row-07.png</x:v>
+        <x:v>set-3_field-1_row-07.png</x:v>
       </x:c>
       <x:c r="E8" s="18" t="str">
-        <x:v>assets/images/set-3/field-2/row-07.png</x:v>
+        <x:v>set-3_field-2_row-07.png</x:v>
       </x:c>
       <x:c r="F8" s="19" t="n">
         <x:v>4</x:v>
@@ -5863,10 +5863,10 @@
         <x:v>Nam libero tempore, cum soluta nobis est eligendi optio cumque nihil impedit quo minus id quod maxime placeat facere possimus.</x:v>
       </x:c>
       <x:c r="D9" s="18" t="str">
-        <x:v>assets/images/set-3/field-1/row-08.png</x:v>
+        <x:v>set-3_field-1_row-08.png</x:v>
       </x:c>
       <x:c r="E9" s="18" t="str">
-        <x:v>assets/images/set-3/field-2/row-08.png</x:v>
+        <x:v>set-3_field-2_row-08.png</x:v>
       </x:c>
       <x:c r="F9" s="19" t="n">
         <x:v>4</x:v>
@@ -5886,10 +5886,10 @@
         <x:v>Lorem ipsum dolor sit amet, consectetur adipiscing elit, sed do eiusmod tempor incididunt ut labore et dolore magna aliqua.</x:v>
       </x:c>
       <x:c r="D10" s="18" t="str">
-        <x:v>assets/images/set-3/field-1/row-09.png</x:v>
+        <x:v>set-3_field-1_row-09.png</x:v>
       </x:c>
       <x:c r="E10" s="18" t="str">
-        <x:v>assets/images/set-3/field-2/row-09.png</x:v>
+        <x:v>set-3_field-2_row-09.png</x:v>
       </x:c>
       <x:c r="F10" s="19" t="n">
         <x:v>4</x:v>
@@ -5909,10 +5909,10 @@
         <x:v>Sed ut perspiciatis unde omnis iste natus error sit voluptatem accusantium doloremque laudantium, totam rem aperiam.</x:v>
       </x:c>
       <x:c r="D11" s="18" t="str">
-        <x:v>assets/images/set-3/field-1/row-10.png</x:v>
+        <x:v>set-3_field-1_row-10.png</x:v>
       </x:c>
       <x:c r="E11" s="18" t="str">
-        <x:v>assets/images/set-3/field-2/row-10.png</x:v>
+        <x:v>set-3_field-2_row-10.png</x:v>
       </x:c>
       <x:c r="F11" s="19" t="n">
         <x:v>4</x:v>
@@ -5932,10 +5932,10 @@
         <x:v>At vero eos et accusamus et iusto odio dignissimos ducimus qui blanditiis praesentium voluptatum deleniti atque corrupti.</x:v>
       </x:c>
       <x:c r="D12" s="18" t="str">
-        <x:v>assets/images/set-3/field-1/row-11.png</x:v>
+        <x:v>set-3_field-1_row-11.png</x:v>
       </x:c>
       <x:c r="E12" s="18" t="str">
-        <x:v>assets/images/set-3/field-2/row-11.png</x:v>
+        <x:v>set-3_field-2_row-11.png</x:v>
       </x:c>
       <x:c r="F12" s="19" t="n">
         <x:v>4</x:v>
@@ -5955,10 +5955,10 @@
         <x:v>Ut enim ad minima veniam, quis nostrum exercitationem ullam corporis suscipit laboriosam, nisi ut aliquid ex ea commodi consequatur.</x:v>
       </x:c>
       <x:c r="D13" s="18" t="str">
-        <x:v>assets/images/set-3/field-1/row-12.png</x:v>
+        <x:v>set-3_field-1_row-12.png</x:v>
       </x:c>
       <x:c r="E13" s="18" t="str">
-        <x:v>assets/images/set-3/field-2/row-12.png</x:v>
+        <x:v>set-3_field-2_row-12.png</x:v>
       </x:c>
       <x:c r="F13" s="19" t="n">
         <x:v>4</x:v>
@@ -5978,10 +5978,10 @@
         <x:v>Nam libero tempore, cum soluta nobis est eligendi optio cumque nihil impedit quo minus id quod maxime placeat facere possimus.</x:v>
       </x:c>
       <x:c r="D14" s="18" t="str">
-        <x:v>assets/images/set-3/field-1/row-13.png</x:v>
+        <x:v>set-3_field-1_row-13.png</x:v>
       </x:c>
       <x:c r="E14" s="18" t="str">
-        <x:v>assets/images/set-3/field-2/row-13.png</x:v>
+        <x:v>set-3_field-2_row-13.png</x:v>
       </x:c>
       <x:c r="F14" s="19" t="n">
         <x:v>4</x:v>
@@ -6001,10 +6001,10 @@
         <x:v>Lorem ipsum dolor sit amet, consectetur adipiscing elit, sed do eiusmod tempor incididunt ut labore et dolore magna aliqua.</x:v>
       </x:c>
       <x:c r="D15" s="18" t="str">
-        <x:v>assets/images/set-3/field-1/row-14.png</x:v>
+        <x:v>set-3_field-1_row-14.png</x:v>
       </x:c>
       <x:c r="E15" s="18" t="str">
-        <x:v>assets/images/set-3/field-2/row-14.png</x:v>
+        <x:v>set-3_field-2_row-14.png</x:v>
       </x:c>
       <x:c r="F15" s="19" t="n">
         <x:v>4</x:v>
@@ -6024,10 +6024,10 @@
         <x:v>Sed ut perspiciatis unde omnis iste natus error sit voluptatem accusantium doloremque laudantium, totam rem aperiam.</x:v>
       </x:c>
       <x:c r="D16" s="18" t="str">
-        <x:v>assets/images/set-3/field-1/row-15.png</x:v>
+        <x:v>set-3_field-1_row-15.png</x:v>
       </x:c>
       <x:c r="E16" s="18" t="str">
-        <x:v>assets/images/set-3/field-2/row-15.png</x:v>
+        <x:v>set-3_field-2_row-15.png</x:v>
       </x:c>
       <x:c r="F16" s="19" t="n">
         <x:v>4</x:v>
@@ -6047,10 +6047,10 @@
         <x:v>At vero eos et accusamus et iusto odio dignissimos ducimus qui blanditiis praesentium voluptatum deleniti atque corrupti.</x:v>
       </x:c>
       <x:c r="D17" s="18" t="str">
-        <x:v>assets/images/set-3/field-1/row-16.png</x:v>
+        <x:v>set-3_field-1_row-16.png</x:v>
       </x:c>
       <x:c r="E17" s="18" t="str">
-        <x:v>assets/images/set-3/field-2/row-16.png</x:v>
+        <x:v>set-3_field-2_row-16.png</x:v>
       </x:c>
       <x:c r="F17" s="19" t="n">
         <x:v>4</x:v>
@@ -6070,10 +6070,10 @@
         <x:v>Ut enim ad minima veniam, quis nostrum exercitationem ullam corporis suscipit laboriosam, nisi ut aliquid ex ea commodi consequatur.</x:v>
       </x:c>
       <x:c r="D18" s="18" t="str">
-        <x:v>assets/images/set-3/field-1/row-17.png</x:v>
+        <x:v>set-3_field-1_row-17.png</x:v>
       </x:c>
       <x:c r="E18" s="18" t="str">
-        <x:v>assets/images/set-3/field-2/row-17.png</x:v>
+        <x:v>set-3_field-2_row-17.png</x:v>
       </x:c>
       <x:c r="F18" s="19" t="n">
         <x:v>4</x:v>
@@ -6093,10 +6093,10 @@
         <x:v>Nam libero tempore, cum soluta nobis est eligendi optio cumque nihil impedit quo minus id quod maxime placeat facere possimus.</x:v>
       </x:c>
       <x:c r="D19" s="18" t="str">
-        <x:v>assets/images/set-3/field-1/row-18.png</x:v>
+        <x:v>set-3_field-1_row-18.png</x:v>
       </x:c>
       <x:c r="E19" s="18" t="str">
-        <x:v>assets/images/set-3/field-2/row-18.png</x:v>
+        <x:v>set-3_field-2_row-18.png</x:v>
       </x:c>
       <x:c r="F19" s="19" t="n">
         <x:v>4</x:v>
@@ -6116,10 +6116,10 @@
         <x:v>Lorem ipsum dolor sit amet, consectetur adipiscing elit, sed do eiusmod tempor incididunt ut labore et dolore magna aliqua.</x:v>
       </x:c>
       <x:c r="D20" s="18" t="str">
-        <x:v>assets/images/set-3/field-1/row-19.png</x:v>
+        <x:v>set-3_field-1_row-19.png</x:v>
       </x:c>
       <x:c r="E20" s="18" t="str">
-        <x:v>assets/images/set-3/field-2/row-19.png</x:v>
+        <x:v>set-3_field-2_row-19.png</x:v>
       </x:c>
       <x:c r="F20" s="19" t="n">
         <x:v>4</x:v>
@@ -6139,10 +6139,10 @@
         <x:v>Sed ut perspiciatis unde omnis iste natus error sit voluptatem accusantium doloremque laudantium, totam rem aperiam.</x:v>
       </x:c>
       <x:c r="D21" s="18" t="str">
-        <x:v>assets/images/set-3/field-1/row-20.png</x:v>
+        <x:v>set-3_field-1_row-20.png</x:v>
       </x:c>
       <x:c r="E21" s="18" t="str">
-        <x:v>assets/images/set-3/field-2/row-20.png</x:v>
+        <x:v>set-3_field-2_row-20.png</x:v>
       </x:c>
       <x:c r="F21" s="19" t="n">
         <x:v>4</x:v>
@@ -6162,10 +6162,10 @@
         <x:v>At vero eos et accusamus et iusto odio dignissimos ducimus qui blanditiis praesentium voluptatum deleniti atque corrupti.</x:v>
       </x:c>
       <x:c r="D22" s="18" t="str">
-        <x:v>assets/images/set-3/field-1/row-21.png</x:v>
+        <x:v>set-3_field-1_row-21.png</x:v>
       </x:c>
       <x:c r="E22" s="18" t="str">
-        <x:v>assets/images/set-3/field-2/row-21.png</x:v>
+        <x:v>set-3_field-2_row-21.png</x:v>
       </x:c>
       <x:c r="F22" s="19" t="n">
         <x:v>4</x:v>
@@ -6185,10 +6185,10 @@
         <x:v>Ut enim ad minima veniam, quis nostrum exercitationem ullam corporis suscipit laboriosam, nisi ut aliquid ex ea commodi consequatur.</x:v>
       </x:c>
       <x:c r="D23" s="18" t="str">
-        <x:v>assets/images/set-3/field-1/row-22.png</x:v>
+        <x:v>set-3_field-1_row-22.png</x:v>
       </x:c>
       <x:c r="E23" s="18" t="str">
-        <x:v>assets/images/set-3/field-2/row-22.png</x:v>
+        <x:v>set-3_field-2_row-22.png</x:v>
       </x:c>
       <x:c r="F23" s="19" t="n">
         <x:v>4</x:v>
@@ -6208,10 +6208,10 @@
         <x:v>Nam libero tempore, cum soluta nobis est eligendi optio cumque nihil impedit quo minus id quod maxime placeat facere possimus.</x:v>
       </x:c>
       <x:c r="D24" s="18" t="str">
-        <x:v>assets/images/set-3/field-1/row-23.png</x:v>
+        <x:v>set-3_field-1_row-23.png</x:v>
       </x:c>
       <x:c r="E24" s="18" t="str">
-        <x:v>assets/images/set-3/field-2/row-23.png</x:v>
+        <x:v>set-3_field-2_row-23.png</x:v>
       </x:c>
       <x:c r="F24" s="19" t="n">
         <x:v>4</x:v>
@@ -6231,10 +6231,10 @@
         <x:v>Lorem ipsum dolor sit amet, consectetur adipiscing elit, sed do eiusmod tempor incididunt ut labore et dolore magna aliqua.</x:v>
       </x:c>
       <x:c r="D25" s="18" t="str">
-        <x:v>assets/images/set-3/field-1/row-24.png</x:v>
+        <x:v>set-3_field-1_row-24.png</x:v>
       </x:c>
       <x:c r="E25" s="18" t="str">
-        <x:v>assets/images/set-3/field-2/row-24.png</x:v>
+        <x:v>set-3_field-2_row-24.png</x:v>
       </x:c>
       <x:c r="F25" s="19" t="n">
         <x:v>4</x:v>
@@ -6254,10 +6254,10 @@
         <x:v>Sed ut perspiciatis unde omnis iste natus error sit voluptatem accusantium doloremque laudantium, totam rem aperiam.</x:v>
       </x:c>
       <x:c r="D26" s="21" t="str">
-        <x:v>assets/images/set-3/field-1/row-25.png</x:v>
+        <x:v>set-3_field-1_row-25.png</x:v>
       </x:c>
       <x:c r="E26" s="21" t="str">
-        <x:v>assets/images/set-3/field-2/row-25.png</x:v>
+        <x:v>set-3_field-2_row-25.png</x:v>
       </x:c>
       <x:c r="F26" s="22" t="n">
         <x:v>4</x:v>
